--- a/data/trans_camb/P16A08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,22</t>
+          <t>-0,53; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,36</t>
+          <t>-0,67; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,33</t>
+          <t>-1,48; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,34</t>
+          <t>-0,84; 2,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,07</t>
+          <t>-1,36; 1,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,39</t>
+          <t>-1,52; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,9</t>
+          <t>-0,18; 1,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,72</t>
+          <t>-0,46; 1,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,88</t>
+          <t>-1,13; 0,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 151,47</t>
+          <t>-25,72; 146,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 176,72</t>
+          <t>-29,08; 165,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,15; 97,18</t>
+          <t>-63,72; 98,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 83,12</t>
+          <t>-19,26; 81,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 69,16</t>
+          <t>-33,28; 61,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 50,8</t>
+          <t>-36,45; 47,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 77,2</t>
+          <t>-5,72; 79,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 70,95</t>
+          <t>-15,96; 66,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 36,09</t>
+          <t>-34,58; 41,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,32</t>
+          <t>0,08; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,69</t>
+          <t>-0,37; 1,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,97</t>
+          <t>0,06; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,31</t>
+          <t>0,43; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,0</t>
+          <t>0,19; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 14,28</t>
+          <t>-0,19; 14,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,39</t>
+          <t>0,54; 2,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,04</t>
+          <t>0,19; 1,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,75</t>
+          <t>0,63; 8,85</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 140,92</t>
+          <t>0,11; 146,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 105,28</t>
+          <t>-15,61; 112,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 178,0</t>
+          <t>3,04; 171,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 96,12</t>
+          <t>8,14; 95,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 91,1</t>
+          <t>3,73; 87,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 351,15</t>
+          <t>-2,66; 395,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 89,59</t>
+          <t>14,46; 87,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 76,42</t>
+          <t>6,38; 74,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 257,08</t>
+          <t>17,92; 295,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,16</t>
+          <t>-1,61; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,11</t>
+          <t>-2,16; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,82</t>
+          <t>-3,75; 1,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 6,17</t>
+          <t>-0,04; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,02</t>
+          <t>-0,03; 6,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,83</t>
+          <t>-0,84; 4,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,25</t>
+          <t>0,09; 4,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,71</t>
+          <t>-0,32; 3,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,76</t>
+          <t>-1,71; 1,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 145,31</t>
+          <t>-35,42; 143,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 110,07</t>
+          <t>-42,49; 102,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,3; 40,25</t>
+          <t>-70,77; 43,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 219,11</t>
+          <t>-2,75; 221,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 208,49</t>
+          <t>-5,31; 219,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 150,59</t>
+          <t>-15,91; 174,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 140,16</t>
+          <t>0,44; 142,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 112,03</t>
+          <t>-6,39; 113,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 54,95</t>
+          <t>-33,11; 56,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,87</t>
+          <t>0,16; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,48</t>
+          <t>-0,04; 1,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,78</t>
+          <t>-0,18; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,71</t>
+          <t>0,58; 2,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,5</t>
+          <t>0,25; 2,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,1</t>
+          <t>0,23; 9,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,96</t>
+          <t>0,66; 2,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,78</t>
+          <t>0,39; 1,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,52</t>
+          <t>0,46; 4,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 91,51</t>
+          <t>4,83; 98,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 71,39</t>
+          <t>-1,82; 80,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 89,5</t>
+          <t>-6,0; 88,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,12; 81,13</t>
+          <t>13,23; 75,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 73,62</t>
+          <t>6,37; 69,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,23; 261,76</t>
+          <t>4,85; 233,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,77; 68,55</t>
+          <t>17,91; 69,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 60,62</t>
+          <t>10,27; 63,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,05; 168,38</t>
+          <t>13,94; 164,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,18</t>
+          <t>-0,61; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,3</t>
+          <t>-0,66; 2,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,43</t>
+          <t>-1,59; 1,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,41</t>
+          <t>-0,85; 2,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,97</t>
+          <t>-1,35; 2,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,36</t>
+          <t>-1,3; 1,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,93</t>
+          <t>-0,16; 2,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,64</t>
+          <t>-0,59; 1,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,97</t>
+          <t>-1,04; 1,05</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-12,16%</t>
+          <t>-15,59%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-4,42%</t>
+          <t>-0,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 146,59</t>
+          <t>-25,62; 158,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 165,68</t>
+          <t>-31,11; 151,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 98,7</t>
+          <t>-66,37; 85,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 81,04</t>
+          <t>-19,94; 75,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 61,98</t>
+          <t>-30,58; 68,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 47,47</t>
+          <t>-31,22; 52,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 79,57</t>
+          <t>-5,26; 89,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 66,66</t>
+          <t>-17,85; 69,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 41,2</t>
+          <t>-31,56; 42,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,34</t>
+          <t>0,2; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,82</t>
+          <t>-0,29; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,93</t>
+          <t>0,65; 3,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,39</t>
+          <t>0,15; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,93</t>
+          <t>0,19; 2,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 14,76</t>
+          <t>-0,4; 2,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,44</t>
+          <t>0,49; 2,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,93</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,85</t>
+          <t>0,5; 2,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 146,55</t>
+          <t>7,29; 150,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 112,89</t>
+          <t>-13,04; 125,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 171,95</t>
+          <t>22,63; 188,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 95,45</t>
+          <t>2,81; 93,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 87,09</t>
+          <t>2,67; 89,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 395,85</t>
+          <t>-7,7; 68,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 87,52</t>
+          <t>15,02; 88,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 74,35</t>
+          <t>5,38; 78,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 295,83</t>
+          <t>13,54; 85,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,99</t>
+          <t>-1,86; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,94</t>
+          <t>-2,03; 3,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,08</t>
+          <t>-3,4; 1,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,27</t>
+          <t>-0,02; 6,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,09</t>
+          <t>0,06; 6,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,47</t>
+          <t>-0,9; 4,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,35</t>
+          <t>0,06; 4,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,63</t>
+          <t>-0,13; 3,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,8</t>
+          <t>-1,29; 2,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-34,55%</t>
+          <t>-25,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 143,94</t>
+          <t>-37,69; 139,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 102,15</t>
+          <t>-37,72; 110,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 43,39</t>
+          <t>-63,28; 43,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 221,36</t>
+          <t>-2,84; 224,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 219,8</t>
+          <t>-2,29; 233,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 174,04</t>
+          <t>-18,54; 164,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 142,9</t>
+          <t>-0,34; 145,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 113,68</t>
+          <t>-3,18; 117,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 56,41</t>
+          <t>-26,37; 73,85</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,89</t>
+          <t>0,21; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,6</t>
+          <t>-0,11; 1,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,8</t>
+          <t>0,17; 1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,6</t>
+          <t>0,52; 2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,41</t>
+          <t>0,41; 2,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,61</t>
+          <t>0,13; 1,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,0</t>
+          <t>0,62; 2,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,41; 1,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,85</t>
+          <t>0,38; 1,63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 98,03</t>
+          <t>7,57; 94,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 80,27</t>
+          <t>-3,81; 76,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 88,74</t>
+          <t>5,38; 100,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,23; 75,33</t>
+          <t>11,36; 75,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 69,53</t>
+          <t>8,87; 69,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 233,53</t>
+          <t>3,24; 57,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 69,97</t>
+          <t>17,24; 68,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,27; 63,49</t>
+          <t>11,46; 59,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,94; 164,22</t>
+          <t>11,52; 56,1</t>
         </is>
       </c>
     </row>
